--- a/demo/linelists/DEMO-ondo-aefi-line-list-25-cases.xlsx
+++ b/demo/linelists/DEMO-ondo-aefi-line-list-25-cases.xlsx
@@ -924,7 +924,7 @@
         <v>+2348000000203</v>
       </c>
       <c r="T11" t="str">
-        <v>14/10/2026</v>
+        <v>14/10/2026,</v>
       </c>
     </row>
     <row r="12">
@@ -1186,10 +1186,10 @@
         <v>Temitope Arowolo</v>
       </c>
       <c r="D16" t="str">
-        <v>F</v>
+        <v>Femal</v>
       </c>
       <c r="E16" t="str">
-        <v>11</v>
+        <v>11 years</v>
       </c>
       <c r="F16" t="str">
         <v>Years</v>
@@ -1275,7 +1275,7 @@
         <v>06/10/2026</v>
       </c>
       <c r="M17" t="str">
-        <v>2, 13</v>
+        <v>2, 13,</v>
       </c>
       <c r="N17" t="str">
         <v>Non-serious</v>
@@ -1641,7 +1641,7 @@
         <v>PCV-8841</v>
       </c>
       <c r="K23" t="str">
-        <v>19/10/2026</v>
+        <v>19//10/2026</v>
       </c>
       <c r="L23" t="str">
         <v>20/10/2026</v>
@@ -1868,10 +1868,10 @@
         <v>Comfort Olaniyan</v>
       </c>
       <c r="D27" t="str">
+        <v>27</v>
+      </c>
+      <c r="E27" t="str">
         <v>F</v>
-      </c>
-      <c r="E27" t="str">
-        <v>27</v>
       </c>
       <c r="F27" t="str">
         <v>Years</v>
@@ -1907,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="Q27" t="str">
-        <v>Funmilayo Adebayo</v>
+        <v>+2348000000201</v>
       </c>
       <c r="R27" t="str">
         <v>Nurse</v>
       </c>
       <c r="S27" t="str">
-        <v>+2348000000201</v>
+        <v>Funmilayo Adebayo</v>
       </c>
       <c r="T27" t="str">
         <v>25/10/2026</v>
